--- a/tests/fixtures/sample_imports/batch_sample.xlsx
+++ b/tests/fixtures/sample_imports/batch_sample.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cevmdtran1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IE_DCS\tests\fixtures\sample_imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9A1DC7-EFCF-4513-846B-F56CDEB10405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF975651-4DB0-4C1F-A975-F55F446A847E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
